--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_48.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3455203.577597876</v>
+        <v>3448226.192905749</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979923</v>
+        <v>9956801.353979915</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979923</v>
+        <v>9956801.353979915</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>18.33383170272989</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -720,7 +720,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>210.6156651633976</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -739,13 +739,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>127.8837310637178</v>
+        <v>341.9742620710306</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>26.34349040625725</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>238.3734759809475</v>
+        <v>406.7884673663621</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606677</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>135.3518862151735</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -988,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>167.1158402638074</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1134,7 +1134,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>178.7541471252643</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1219,13 +1219,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>130.4969705151834</v>
+        <v>182.885439975089</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1447,7 +1447,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>86.93822665041519</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G14" t="n">
         <v>53.75737228701621</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>107.5980768338923</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V15" t="n">
         <v>64.51066719152016</v>
@@ -1747,7 +1747,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X15" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>49.39139276613435</v>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X18" t="n">
         <v>69.86273944538755</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>115.0662319853481</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
         <v>11.09991244551929</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2209,7 +2209,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U21" t="n">
         <v>50.21035976018675</v>
@@ -2334,7 +2334,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>84.14143263308497</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V24" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
         <v>82.37314290982852</v>
@@ -2461,7 +2461,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="25">
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2635,13 +2635,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>64.74007562773993</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>122.4329129537</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U29" t="n">
         <v>299.2212965486107</v>
@@ -2881,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>62.67776252544248</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2926,13 +2926,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X30" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>49.39139276613435</v>
@@ -3033,7 +3033,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E32" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F32" t="n">
         <v>54.88962870801186</v>
@@ -3087,7 +3087,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X32" t="n">
         <v>242.2818334606677</v>
@@ -3118,13 +3118,13 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3154,13 +3154,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U33" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V33" t="n">
         <v>64.51066719152016</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3343,19 +3343,19 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>75.83998807325922</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>73.04152018756567</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>80.50967533902147</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>127.1884297169627</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>49.39139276613435</v>
+        <v>122.4329129537</v>
       </c>
     </row>
     <row r="43">
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4057,7 +4057,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4108,10 +4108,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>114.9504353879267</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4321,46 +4321,46 @@
         <v>33.68</v>
       </c>
       <c r="J2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="K2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="L2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="M2" t="n">
-        <v>424.9891130376558</v>
+        <v>33.68</v>
       </c>
       <c r="N2" t="n">
-        <v>841.7791130376559</v>
+        <v>450.47</v>
       </c>
       <c r="O2" t="n">
-        <v>1258.569113037656</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1675.359113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1684</v>
+        <v>1665.480978078051</v>
       </c>
       <c r="S2" t="n">
-        <v>1588.193769896644</v>
+        <v>1569.674747974694</v>
       </c>
       <c r="T2" t="n">
-        <v>1399.632576231427</v>
+        <v>1381.113554309478</v>
       </c>
       <c r="U2" t="n">
-        <v>1147.893892848992</v>
+        <v>1129.374870927043</v>
       </c>
       <c r="V2" t="n">
-        <v>915.7211411653319</v>
+        <v>897.2021192433824</v>
       </c>
       <c r="W2" t="n">
-        <v>674.9398522956878</v>
+        <v>656.4208303737385</v>
       </c>
       <c r="X2" t="n">
         <v>462.1967561710438</v>
@@ -4382,19 +4382,19 @@
         <v>725.2419790837811</v>
       </c>
       <c r="D3" t="n">
-        <v>596.0664931608338</v>
+        <v>379.8134315372855</v>
       </c>
       <c r="E3" t="n">
-        <v>596.0664931608338</v>
+        <v>33.68</v>
       </c>
       <c r="F3" t="n">
-        <v>252.9995817084329</v>
+        <v>33.68</v>
       </c>
       <c r="G3" t="n">
-        <v>252.9995817084329</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
-        <v>252.9995817084329</v>
+        <v>33.68</v>
       </c>
       <c r="I3" t="n">
         <v>33.68</v>
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>752.1604946826228</v>
+        <v>693.684981203141</v>
       </c>
       <c r="C4" t="n">
-        <v>752.1604946826228</v>
+        <v>819.6869870215768</v>
       </c>
       <c r="D4" t="n">
-        <v>865.4796388076229</v>
+        <v>925.6444408330618</v>
       </c>
       <c r="E4" t="n">
-        <v>865.4796388076229</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="F4" t="n">
-        <v>865.4796388076229</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="G4" t="n">
-        <v>865.4796388076229</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="H4" t="n">
-        <v>1034.996223967021</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="I4" t="n">
-        <v>1256.129102903104</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J4" t="n">
         <v>1434.122809139956</v>
@@ -4509,22 +4509,22 @@
         <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>70.93025509417312</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>317.4814477324597</v>
+        <v>259.005934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>317.4814477324597</v>
+        <v>259.005934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>489.3723659921371</v>
+        <v>430.8968525126554</v>
       </c>
       <c r="X4" t="n">
-        <v>640.4031570163306</v>
+        <v>581.9276435368489</v>
       </c>
       <c r="Y4" t="n">
-        <v>640.4031570163306</v>
+        <v>581.9276435368489</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285.4463380542246</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E5" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G5" t="n">
-        <v>211.8867172615575</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I5" t="n">
         <v>33.68</v>
@@ -4564,19 +4564,19 @@
         <v>33.68</v>
       </c>
       <c r="L5" t="n">
-        <v>33.68</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>450.47</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>867.26</v>
+        <v>1267.21</v>
       </c>
       <c r="O5" t="n">
-        <v>1284.05</v>
+        <v>1684</v>
       </c>
       <c r="P5" t="n">
-        <v>1284.05</v>
+        <v>1684</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4597,13 +4597,13 @@
         <v>915.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>480.7157780929932</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>900.0695195792149</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="C6" t="n">
-        <v>900.0695195792149</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="D6" t="n">
-        <v>548.6173105916364</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="E6" t="n">
-        <v>202.4838790543509</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="F6" t="n">
-        <v>202.4838790543509</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="G6" t="n">
-        <v>202.4838790543509</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="H6" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="I6" t="n">
         <v>33.68</v>
@@ -4658,31 +4658,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S6" t="n">
-        <v>973.1146453614743</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T6" t="n">
-        <v>967.7027613033796</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U6" t="n">
-        <v>967.4902766971303</v>
+        <v>792.6627362016965</v>
       </c>
       <c r="V6" t="n">
-        <v>952.8330371097362</v>
+        <v>778.0054966143024</v>
       </c>
       <c r="W6" t="n">
-        <v>920.1328927563741</v>
+        <v>745.3053522609403</v>
       </c>
       <c r="X6" t="n">
-        <v>900.0695195792149</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="Y6" t="n">
-        <v>900.0695195792149</v>
+        <v>725.2419790837811</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>432.0266259816525</v>
+        <v>679.7912225091035</v>
       </c>
       <c r="C7" t="n">
-        <v>558.0286318000883</v>
+        <v>805.7932283275393</v>
       </c>
       <c r="D7" t="n">
-        <v>558.0286318000883</v>
+        <v>919.1123724525394</v>
       </c>
       <c r="E7" t="n">
-        <v>558.0286318000883</v>
+        <v>919.1123724525394</v>
       </c>
       <c r="F7" t="n">
-        <v>682.3896043920238</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="G7" t="n">
-        <v>682.3896043920238</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="H7" t="n">
-        <v>851.9061895514213</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="I7" t="n">
-        <v>1073.039068487504</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J7" t="n">
         <v>1434.122809139956</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>33.68</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>33.68</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>232.501392885946</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="W7" t="n">
-        <v>232.501392885946</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="X7" t="n">
-        <v>383.5321839101395</v>
+        <v>568.0338848428114</v>
       </c>
       <c r="Y7" t="n">
-        <v>432.0266259816525</v>
+        <v>568.0338848428114</v>
       </c>
     </row>
     <row r="8">
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115.3301851396645</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>65.35586368209485</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D8" t="n">
         <v>54.91227202568093</v>
@@ -4819,28 +4819,28 @@
         <v>1684</v>
       </c>
       <c r="R8" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S8" t="n">
-        <v>1418.077616982083</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1229.516423316867</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>977.7777399344324</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>310.5996251784331</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>511.6285532697941</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C9" t="n">
-        <v>511.6285532697941</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="D9" t="n">
-        <v>511.6285532697941</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="E9" t="n">
-        <v>165.4951217325086</v>
+        <v>553.9360880419295</v>
       </c>
       <c r="F9" t="n">
-        <v>33.68</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="G9" t="n">
-        <v>33.68</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="H9" t="n">
         <v>33.68</v>
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>327.3530308546201</v>
+        <v>778.7429323216315</v>
       </c>
       <c r="C10" t="n">
-        <v>453.3550366730559</v>
+        <v>904.7449381400673</v>
       </c>
       <c r="D10" t="n">
-        <v>566.674180798056</v>
+        <v>904.7449381400673</v>
       </c>
       <c r="E10" t="n">
-        <v>684.503085009469</v>
+        <v>1022.57384235148</v>
       </c>
       <c r="F10" t="n">
-        <v>808.8640576014045</v>
+        <v>1022.57384235148</v>
       </c>
       <c r="G10" t="n">
-        <v>962.2706234882897</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="H10" t="n">
-        <v>962.2706234882897</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="I10" t="n">
-        <v>1183.403502424373</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J10" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K10" t="n">
         <v>1544.487243076824</v>
@@ -4983,22 +4983,22 @@
         <v>70.93025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>104.1863925092957</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>104.1863925092957</v>
+        <v>317.4814477324597</v>
       </c>
       <c r="V10" t="n">
-        <v>104.1863925092957</v>
+        <v>516.3028406184058</v>
       </c>
       <c r="W10" t="n">
-        <v>104.1863925092957</v>
+        <v>516.3028406184058</v>
       </c>
       <c r="X10" t="n">
-        <v>104.1863925092957</v>
+        <v>667.3336316425992</v>
       </c>
       <c r="Y10" t="n">
-        <v>215.595693188328</v>
+        <v>778.7429323216315</v>
       </c>
     </row>
     <row r="11">
@@ -5023,34 +5023,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M11" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N11" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5090,19 +5090,19 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D12" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E12" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F12" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="G12" t="n">
-        <v>132.5363905559749</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="H12" t="n">
         <v>44.72</v>
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C13" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F13" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G13" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H13" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I13" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J13" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K13" t="n">
         <v>1921.561060958496</v>
@@ -5220,22 +5220,22 @@
         <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="14">
@@ -5257,13 +5257,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5275,19 +5275,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M14" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N14" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>398.9989442256527</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
         <v>44.72</v>
@@ -5381,19 +5381,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5506,22 +5506,22 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L17" t="n">
-        <v>436.0291130376557</v>
+        <v>1151.54</v>
       </c>
       <c r="M17" t="n">
-        <v>436.0291130376558</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N17" t="n">
-        <v>989.4391130376557</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>1797.400904947332</v>
@@ -5564,22 +5564,22 @@
         <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
-        <v>108.0308712378206</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D18" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5624,13 +5624,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>154.1485167851397</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C19" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D19" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H19" t="n">
         <v>1377.480007433093</v>
@@ -5694,22 +5694,22 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U19" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V19" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W19" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X19" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y19" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>179.7320762183977</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>179.7320762183977</v>
+        <v>44.72</v>
       </c>
       <c r="L20" t="n">
-        <v>179.7320762183977</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M20" t="n">
-        <v>690.5809049473327</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N20" t="n">
-        <v>690.5809049473327</v>
+        <v>1129.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>391.4553531635761</v>
+        <v>1155.090483642537</v>
       </c>
       <c r="C21" t="n">
-        <v>380.2433203903244</v>
+        <v>1143.878450869285</v>
       </c>
       <c r="D21" t="n">
-        <v>380.2433203903244</v>
+        <v>1143.878450869285</v>
       </c>
       <c r="E21" t="n">
-        <v>380.2433203903244</v>
+        <v>1143.878450869285</v>
       </c>
       <c r="F21" t="n">
-        <v>380.2433203903244</v>
+        <v>1143.878450869285</v>
       </c>
       <c r="G21" t="n">
-        <v>380.2433203903244</v>
+        <v>1143.878450869285</v>
       </c>
       <c r="H21" t="n">
-        <v>44.72</v>
+        <v>1080.567579631464</v>
       </c>
       <c r="I21" t="n">
-        <v>44.72</v>
+        <v>1080.567579631464</v>
       </c>
       <c r="J21" t="n">
-        <v>168.6765201752989</v>
+        <v>1204.524099806763</v>
       </c>
       <c r="K21" t="n">
-        <v>357.8693362696823</v>
+        <v>1393.716915901147</v>
       </c>
       <c r="L21" t="n">
-        <v>629.2197978648824</v>
+        <v>1665.067377496347</v>
       </c>
       <c r="M21" t="n">
-        <v>715.3003396077416</v>
+        <v>1751.147919239206</v>
       </c>
       <c r="N21" t="n">
-        <v>848.58062421531</v>
+        <v>1884.428203846775</v>
       </c>
       <c r="O21" t="n">
-        <v>1087.623075899029</v>
+        <v>2123.470655530493</v>
       </c>
       <c r="P21" t="n">
-        <v>1200.152420368536</v>
+        <v>2236</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.152420368536</v>
+        <v>2236</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>2036.733538088506</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>1918.992123982838</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>1509.539835884339</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>1458.822300773039</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>1393.660010680595</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>1310.454815822182</v>
       </c>
       <c r="X21" t="n">
-        <v>557.5741660438614</v>
+        <v>1239.886392139972</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.6838703204934</v>
+        <v>1189.996096416604</v>
       </c>
     </row>
     <row r="22">
@@ -5956,43 +5956,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L23" t="n">
-        <v>179.7320762183977</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M23" t="n">
-        <v>690.5809049473327</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N23" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O23" t="n">
         <v>1797.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
         <v>44.72</v>
@@ -6095,16 +6095,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907175</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H25" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J25" t="n">
         <v>1860.696627021627</v>
@@ -6174,16 +6174,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6193,49 +6193,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H26" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L26" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="M26" t="n">
-        <v>690.5809049473327</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N26" t="n">
-        <v>1243.990904947333</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6244,25 +6244,25 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>398.9989442256527</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C27" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D27" t="n">
-        <v>387.7869114524009</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="E27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
         <v>44.72</v>
@@ -6341,7 +6341,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y27" t="n">
-        <v>433.9045569997199</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="28">
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,22 +6457,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L29" t="n">
         <v>989.4391130376558</v>
       </c>
       <c r="M29" t="n">
-        <v>1500.287941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="N29" t="n">
-        <v>1500.287941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O29" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6484,22 +6484,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6524,7 +6524,7 @@
         <v>108.0308712378207</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6569,10 +6569,10 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>274.6072361907175</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
         <v>204.0388125085078</v>
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E32" t="n">
         <v>213.0600603015712</v>
@@ -6694,19 +6694,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>1542.849113037656</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1500.287941766591</v>
+      </c>
+      <c r="O32" t="n">
         <v>1682.59</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1682.59</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2236</v>
       </c>
       <c r="P32" t="n">
         <v>2236</v>
@@ -6730,13 +6730,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C33" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D33" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E33" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F33" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G33" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H33" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I33" t="n">
         <v>44.72</v>
@@ -6797,25 +6797,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135527</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504074</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W33" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X33" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="34">
@@ -6879,10 +6879,10 @@
         <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U34" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V34" t="n">
         <v>521.9574820108303</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6931,49 +6931,49 @@
         <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>598.13</v>
+        <v>575.7700000000002</v>
       </c>
       <c r="L35" t="n">
-        <v>733.1420762183976</v>
+        <v>1129.18</v>
       </c>
       <c r="M35" t="n">
-        <v>1243.990904947333</v>
+        <v>1129.18</v>
       </c>
       <c r="N35" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6986,16 +6986,16 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>118.4993133207734</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>1151.54</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>1662.388828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N38" t="n">
-        <v>2215.798828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="O38" t="n">
-        <v>2215.798828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="P38" t="n">
-        <v>2215.798828728935</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7232,10 +7232,10 @@
         <v>461.5662247731743</v>
       </c>
       <c r="F39" t="n">
-        <v>380.2433203903244</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7308,7 +7308,7 @@
         <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
         <v>1153.55685638681</v>
@@ -7405,22 +7405,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F42" t="n">
         <v>44.72</v>
@@ -7517,16 +7517,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>444.3729990826727</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="43">
@@ -7536,31 +7536,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K43" t="n">
         <v>1921.561060958496</v>
@@ -7602,10 +7602,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L44" t="n">
-        <v>733.1420762183976</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M44" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="N44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>407.3842417608302</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>396.1722089875784</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7751,19 +7751,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>711.1160588913324</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>645.9537687988877</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W45" t="n">
-        <v>562.7485739404751</v>
+        <v>274.6072361907175</v>
       </c>
       <c r="X45" t="n">
-        <v>492.1801502582655</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>442.2898545348975</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="46">
@@ -7794,7 +7794,7 @@
         <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J46" t="n">
         <v>1860.696627021627</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>491.2478695740924</v>
+        <v>474.2377685639915</v>
       </c>
       <c r="P2" t="n">
         <v>421.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.5508529763179</v>
+        <v>593.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,7 +8207,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="M5" t="n">
         <v>965.2621276423173</v>
@@ -8222,7 +8222,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>576.8125833173845</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8687,16 +8687,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,22 +8918,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O14" t="n">
-        <v>254.3913627391524</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O17" t="n">
-        <v>327.3708917050792</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>171.4188408091284</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
         <v>629.2478695740924</v>
@@ -9407,7 +9407,7 @@
         <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,22 +9623,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M26" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
         <v>1036.248958069835</v>
@@ -9878,10 +9878,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>20.69228354680773</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153925</v>
       </c>
       <c r="N29" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>300.4011642636528</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,22 +10337,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>685.4145387153924</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q32" t="n">
         <v>172.8226843274854</v>
@@ -10574,13 +10574,13 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
+        <v>536.4141414141417</v>
+      </c>
+      <c r="L35" t="n">
         <v>559</v>
       </c>
-      <c r="L35" t="n">
-        <v>136.375834564038</v>
-      </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
@@ -10589,10 +10589,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348954</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q38" t="n">
-        <v>193.2279078336117</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>618.4013691429103</v>
       </c>
       <c r="O41" t="n">
-        <v>370.3619737970638</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -26275,7 +26275,7 @@
         <v>1511252.448399113</v>
       </c>
       <c r="D2" t="n">
-        <v>1511252.448399114</v>
+        <v>1511252.448399113</v>
       </c>
       <c r="E2" t="n">
         <v>1511252.448399113</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359546</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983393</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>737481.0891566036</v>
+        <v>735918.4760631588</v>
       </c>
       <c r="C6" t="n">
-        <v>887705.6049201485</v>
+        <v>886142.9918267034</v>
       </c>
       <c r="D6" t="n">
-        <v>889740.8779181876</v>
+        <v>888178.2648247421</v>
       </c>
       <c r="E6" t="n">
-        <v>576171.0451725778</v>
+        <v>574429.1953594704</v>
       </c>
       <c r="F6" t="n">
-        <v>906689.9405180822</v>
+        <v>904948.0907049746</v>
       </c>
       <c r="G6" t="n">
-        <v>908635.5169862678</v>
+        <v>906893.6671731601</v>
       </c>
       <c r="H6" t="n">
-        <v>910583.7938035688</v>
+        <v>908841.9439904614</v>
       </c>
       <c r="I6" t="n">
-        <v>912534.7904469293</v>
+        <v>910792.9406338217</v>
       </c>
       <c r="J6" t="n">
-        <v>486296.5266485541</v>
+        <v>484554.6768354467</v>
       </c>
       <c r="K6" t="n">
-        <v>916445.0224007739</v>
+        <v>914703.1725876661</v>
       </c>
       <c r="L6" t="n">
-        <v>918404.2979610334</v>
+        <v>916662.4481479254</v>
       </c>
       <c r="M6" t="n">
-        <v>871790.3738570126</v>
+        <v>870048.5240439051</v>
       </c>
       <c r="N6" t="n">
-        <v>922331.2708918657</v>
+        <v>920589.4210787581</v>
       </c>
       <c r="O6" t="n">
-        <v>644299.0101496037</v>
+        <v>642557.1603364963</v>
       </c>
       <c r="P6" t="n">
-        <v>926269.6130006146</v>
+        <v>924527.7631875067</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27014,7 +27014,7 @@
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -27024,11 +27024,11 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
@@ -27036,10 +27036,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -27097,7 +27097,7 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>421</v>
@@ -27112,7 +27112,7 @@
         <v>138</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>232.5447671255646</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27499,7 +27499,7 @@
         <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="Y2" t="n">
         <v>400</v>
@@ -27518,13 +27518,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>220.0539558339848</v>
+        <v>5.963424826672053</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27594,13 +27594,13 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
+        <v>392.5639491782676</v>
+      </c>
+      <c r="E4" t="n">
         <v>400</v>
-      </c>
-      <c r="E4" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>215.0605712973744</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27645,10 +27645,10 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27733,7 +27733,7 @@
         <v>400</v>
       </c>
       <c r="W5" t="n">
-        <v>400</v>
+        <v>231.5850086145854</v>
       </c>
       <c r="X5" t="n">
         <v>400</v>
@@ -27755,10 +27755,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>212.5858006825291</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27767,10 +27767,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>165.0522469226138</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>310.5514817448013</v>
       </c>
       <c r="Y7" t="n">
-        <v>336.4496377701826</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27913,7 +27913,7 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -27998,13 +27998,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>209.1392718226934</v>
+        <v>156.7508023627879</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>266.1544816223325</v>
+      </c>
+      <c r="H10" t="n">
         <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>400</v>
-      </c>
-      <c r="H10" t="n">
-        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="K10" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28119,19 +28119,19 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>243.616624501331</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28159,13 +28159,13 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
         <v>350</v>
       </c>
       <c r="C12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -28238,10 +28238,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>245.2298605360059</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28329,7 +28329,7 @@
         <v>350</v>
       </c>
       <c r="K13" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L13" t="n">
         <v>350</v>
@@ -28356,7 +28356,7 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
@@ -28393,7 +28393,7 @@
         <v>350</v>
       </c>
       <c r="F14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G14" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28472,7 +28472,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28517,7 +28517,7 @@
         <v>350</v>
       </c>
       <c r="U15" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -28526,7 +28526,7 @@
         <v>350</v>
       </c>
       <c r="X15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>350</v>
@@ -28697,13 +28697,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
@@ -28718,7 +28718,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>154.4486233659061</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28760,7 +28760,7 @@
         <v>350</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X18" t="n">
         <v>350</v>
@@ -28794,43 +28794,43 @@
         <v>350</v>
       </c>
       <c r="H19" t="n">
+        <v>350</v>
+      </c>
+      <c r="I19" t="n">
+        <v>350</v>
+      </c>
+      <c r="J19" t="n">
+        <v>350</v>
+      </c>
+      <c r="K19" t="n">
+        <v>350</v>
+      </c>
+      <c r="L19" t="n">
+        <v>350</v>
+      </c>
+      <c r="M19" t="n">
+        <v>350</v>
+      </c>
+      <c r="N19" t="n">
+        <v>350</v>
+      </c>
+      <c r="O19" t="n">
+        <v>350</v>
+      </c>
+      <c r="P19" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>350</v>
+      </c>
+      <c r="R19" t="n">
+        <v>350</v>
+      </c>
+      <c r="S19" t="n">
+        <v>350</v>
+      </c>
+      <c r="T19" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="I19" t="n">
-        <v>350</v>
-      </c>
-      <c r="J19" t="n">
-        <v>350</v>
-      </c>
-      <c r="K19" t="n">
-        <v>350</v>
-      </c>
-      <c r="L19" t="n">
-        <v>350</v>
-      </c>
-      <c r="M19" t="n">
-        <v>350</v>
-      </c>
-      <c r="N19" t="n">
-        <v>350</v>
-      </c>
-      <c r="O19" t="n">
-        <v>350</v>
-      </c>
-      <c r="P19" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>350</v>
-      </c>
-      <c r="R19" t="n">
-        <v>350</v>
-      </c>
-      <c r="S19" t="n">
-        <v>350</v>
-      </c>
-      <c r="T19" t="n">
-        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="C21" t="n">
         <v>350</v>
@@ -28952,7 +28952,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -28988,7 +28988,7 @@
         <v>350</v>
       </c>
       <c r="T21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>350</v>
@@ -29113,7 +29113,7 @@
         <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29183,7 +29183,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
@@ -29231,7 +29231,7 @@
         <v>350</v>
       </c>
       <c r="V24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>350</v>
@@ -29240,7 +29240,7 @@
         <v>350</v>
       </c>
       <c r="Y24" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="25">
@@ -29274,7 +29274,7 @@
         <v>350</v>
       </c>
       <c r="J25" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K25" t="n">
         <v>350</v>
@@ -29310,7 +29310,7 @@
         <v>350</v>
       </c>
       <c r="V25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29414,13 +29414,13 @@
         <v>350</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>325.7395358750273</v>
@@ -29477,7 +29477,7 @@
         <v>350</v>
       </c>
       <c r="Y27" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28">
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29620,7 +29620,7 @@
         <v>350</v>
       </c>
       <c r="T29" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U29" t="n">
         <v>350</v>
@@ -29660,10 +29660,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>263.0617733495849</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29705,13 +29705,13 @@
         <v>350</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W30" t="n">
         <v>350</v>
       </c>
       <c r="X30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>350</v>
@@ -29812,7 +29812,7 @@
         <v>350</v>
       </c>
       <c r="E32" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="F32" t="n">
         <v>350</v>
@@ -29866,7 +29866,7 @@
         <v>350</v>
       </c>
       <c r="W32" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X32" t="n">
         <v>350</v>
@@ -29897,13 +29897,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>130.1881592409333</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29933,13 +29933,13 @@
         <v>350</v>
       </c>
       <c r="S33" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T33" t="n">
         <v>350</v>
       </c>
       <c r="U33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>350</v>
@@ -30015,13 +30015,13 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
       </c>
       <c r="V34" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W34" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30122,19 +30122,19 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>252.6980156874617</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C37" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30368,13 +30368,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>259.1265669988554</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30444,10 +30444,10 @@
         <v>350</v>
       </c>
       <c r="E40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="F40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G40" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30605,7 +30605,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
@@ -30653,7 +30653,7 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
     </row>
     <row r="43">
@@ -30699,7 +30699,7 @@
         <v>350</v>
       </c>
       <c r="K43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L43" t="n">
         <v>350</v>
@@ -30738,7 +30738,7 @@
         <v>350</v>
       </c>
       <c r="X43" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30836,7 +30836,7 @@
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30887,10 +30887,10 @@
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -30930,10 +30930,10 @@
         <v>350</v>
       </c>
       <c r="I46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="J46" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34758,13 +34758,13 @@
         <v>421</v>
       </c>
       <c r="O2" t="n">
-        <v>421</v>
+        <v>403.989898989899</v>
       </c>
       <c r="P2" t="n">
         <v>421</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.728168648832536</v>
+        <v>421</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,13 +34880,13 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>107.0277311227122</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34901,7 +34901,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>179.7916224614666</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34931,10 +34931,10 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34986,7 +34986,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="M5" t="n">
         <v>421</v>
@@ -35001,7 +35001,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>403.989898989899</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -35138,7 +35138,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>63.10783631469374</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.98428492072025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>21.1106087808025</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,19 +35405,19 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>33.59205799507333</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -35466,16 +35466,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35615,7 +35615,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K13" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
@@ -35697,22 +35697,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O14" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O17" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36080,7 +36080,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H19" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I19" t="n">
         <v>173.3665443798817</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O20" t="n">
         <v>559</v>
@@ -36186,7 +36186,7 @@
         <v>559</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,22 +36402,22 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36560,7 +36560,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J25" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K25" t="n">
         <v>61.47922619885696</v>
@@ -36596,7 +36596,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M26" t="n">
-        <v>257.1230221309867</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
         <v>559</v>
@@ -36657,10 +36657,10 @@
         <v>559</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>141.1524110730752</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>559</v>
       </c>
-      <c r="M29" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,22 +37116,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N32" t="n">
         <v>559</v>
       </c>
-      <c r="L32" t="n">
+      <c r="O32" t="n">
+        <v>184.1434931650599</v>
+      </c>
+      <c r="P32" t="n">
         <v>559</v>
-      </c>
-      <c r="M32" t="n">
-        <v>141.1524110730751</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>559</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37301,13 +37301,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V34" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W34" t="n">
         <v>123.6271901612903</v>
@@ -37353,13 +37353,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>536.4141414141417</v>
+      </c>
+      <c r="L35" t="n">
         <v>559</v>
       </c>
-      <c r="L35" t="n">
-        <v>136.375834564038</v>
-      </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
@@ -37368,10 +37368,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C37" t="n">
         <v>77.27475335195533</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
+        <v>184.1434931650601</v>
+      </c>
+      <c r="O38" t="n">
         <v>559</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q38" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37730,10 +37730,10 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>69.01909516304346</v>
+        <v>61.23042579717762</v>
       </c>
       <c r="F40" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G40" t="n">
         <v>104.95612715847</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
+        <v>141.1524110730751</v>
+      </c>
+      <c r="O41" t="n">
         <v>559</v>
       </c>
-      <c r="O41" t="n">
-        <v>300.1141042229714</v>
-      </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37985,7 +37985,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38024,7 +38024,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y43" t="n">
         <v>62.53464715053764</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38216,10 +38216,10 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I46" t="n">
-        <v>173.3665443798817</v>
+        <v>165.577875014016</v>
       </c>
       <c r="J46" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
